--- a/datos.xlsx
+++ b/datos.xlsx
@@ -1,42 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuarios\jmadrids\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuarios\jmadrids\Desktop\dashboard_sentencias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633BBCBB-D7D1-43A9-A045-63EF7BF95B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9540774C-A487-4F9F-9C79-9D23EE698222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{19D2D07E-EE3D-436A-A448-0E9746A10E17}"/>
+    <workbookView xWindow="10215" yWindow="1065" windowWidth="17310" windowHeight="14790" xr2:uid="{19D2D07E-EE3D-436A-A448-0E9746A10E17}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="143">
   <si>
     <t>EXP</t>
   </si>
@@ -450,13 +439,28 @@
   </si>
   <si>
     <t>00101-2025-0-5401-SP-ED-01</t>
+  </si>
+  <si>
+    <t>NOMBRE_ARCHIVO</t>
+  </si>
+  <si>
+    <t>ENLACE_PDF</t>
+  </si>
+  <si>
+    <t>45-2019-0</t>
+  </si>
+  <si>
+    <t>45-2019-0.pdf</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1aeWFVOIxOZyGtk5XBYG7o-p4v9fDIycA/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -477,6 +481,14 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -486,7 +498,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -509,11 +521,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -536,11 +560,36 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -889,7 +938,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{658BD17B-64B8-45C7-ADE1-042181653E12}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
@@ -899,9 +948,10 @@
     <col min="5" max="5" width="20.375" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15">
+    <row r="1" spans="1:9" ht="15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -923,8 +973,14 @@
       <c r="G1" s="8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -945,7 +1001,7 @@
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -966,7 +1022,7 @@
       </c>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
@@ -987,7 +1043,7 @@
       </c>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -1008,7 +1064,7 @@
       </c>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -1029,7 +1085,7 @@
       </c>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -1050,7 +1106,7 @@
       </c>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>27</v>
       </c>
@@ -1071,7 +1127,7 @@
       </c>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -1092,7 +1148,7 @@
       </c>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -1113,7 +1169,7 @@
       </c>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
@@ -1134,7 +1190,7 @@
       </c>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>31</v>
       </c>
@@ -1155,7 +1211,7 @@
       </c>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
         <v>32</v>
       </c>
@@ -1176,7 +1232,7 @@
       </c>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
         <v>33</v>
       </c>
@@ -1197,7 +1253,7 @@
       </c>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
@@ -1218,7 +1274,7 @@
       </c>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
         <v>35</v>
       </c>
@@ -3259,7 +3315,7 @@
       </c>
       <c r="G112" s="2"/>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:9">
       <c r="A113" s="6" t="s">
         <v>130</v>
       </c>
@@ -3280,7 +3336,7 @@
       </c>
       <c r="G113" s="2"/>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:9">
       <c r="A114" s="6" t="s">
         <v>131</v>
       </c>
@@ -3301,7 +3357,7 @@
       </c>
       <c r="G114" s="2"/>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:9">
       <c r="A115" s="6" t="s">
         <v>132</v>
       </c>
@@ -3322,7 +3378,7 @@
       </c>
       <c r="G115" s="2"/>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:9">
       <c r="A116" s="6" t="s">
         <v>133</v>
       </c>
@@ -3343,7 +3399,7 @@
       </c>
       <c r="G116" s="2"/>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:9">
       <c r="A117" s="6" t="s">
         <v>134</v>
       </c>
@@ -3364,7 +3420,7 @@
       </c>
       <c r="G117" s="2"/>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:9">
       <c r="A118" s="6" t="s">
         <v>135</v>
       </c>
@@ -3385,7 +3441,7 @@
       </c>
       <c r="G118" s="2"/>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:9">
       <c r="A119" s="6" t="s">
         <v>136</v>
       </c>
@@ -3406,7 +3462,7 @@
       </c>
       <c r="G119" s="2"/>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:9">
       <c r="A120" s="6" t="s">
         <v>137</v>
       </c>
@@ -3427,16 +3483,22 @@
       </c>
       <c r="G120" s="2"/>
     </row>
+    <row r="121" spans="1:9">
+      <c r="A121" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="H121" t="s">
+        <v>141</v>
+      </c>
+      <c r="I121" s="12" t="s">
+        <v>142</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>OR(CELL("fila")=ROW(), CELL("columna")=COLUMN())</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="I121" r:id="rId1" xr:uid="{75C2E809-4C7C-4D4D-9961-102B217AF839}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuarios\jmadrids\Desktop\dashboard_sentencias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9540774C-A487-4F9F-9C79-9D23EE698222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80889F43-6EEE-44A0-A643-34AD8A984918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10215" yWindow="1065" windowWidth="17310" windowHeight="14790" xr2:uid="{19D2D07E-EE3D-436A-A448-0E9746A10E17}"/>
+    <workbookView xWindow="1560" yWindow="1410" windowWidth="17310" windowHeight="14790" xr2:uid="{19D2D07E-EE3D-436A-A448-0E9746A10E17}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="143">
   <si>
     <t>EXP</t>
   </si>
@@ -447,13 +447,13 @@
     <t>ENLACE_PDF</t>
   </si>
   <si>
-    <t>45-2019-0</t>
-  </si>
-  <si>
     <t>45-2019-0.pdf</t>
   </si>
   <si>
     <t>https://drive.google.com/file/d/1aeWFVOIxOZyGtk5XBYG7o-p4v9fDIycA/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>45-2019-0-5401</t>
   </si>
 </sst>
 </file>
@@ -498,7 +498,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -521,23 +521,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -560,54 +549,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -973,10 +921,10 @@
       <c r="G1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>139</v>
       </c>
     </row>
@@ -1000,6 +948,8 @@
         <v>3</v>
       </c>
       <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
@@ -1021,6 +971,8 @@
         <v>3</v>
       </c>
       <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
@@ -1042,6 +994,8 @@
         <v>3</v>
       </c>
       <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
@@ -1063,6 +1017,8 @@
         <v>3</v>
       </c>
       <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
@@ -1084,6 +1040,8 @@
         <v>3</v>
       </c>
       <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
@@ -1105,6 +1063,8 @@
         <v>3</v>
       </c>
       <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
@@ -1126,6 +1086,8 @@
         <v>3</v>
       </c>
       <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
@@ -1147,6 +1109,8 @@
         <v>3</v>
       </c>
       <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
@@ -1168,6 +1132,8 @@
         <v>3</v>
       </c>
       <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
@@ -1189,6 +1155,8 @@
         <v>3</v>
       </c>
       <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
@@ -1210,6 +1178,8 @@
         <v>3</v>
       </c>
       <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
@@ -1231,6 +1201,8 @@
         <v>3</v>
       </c>
       <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
@@ -1252,6 +1224,8 @@
         <v>3</v>
       </c>
       <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
@@ -1273,6 +1247,8 @@
         <v>3</v>
       </c>
       <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
@@ -1294,8 +1270,10 @@
         <v>3</v>
       </c>
       <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
         <v>36</v>
       </c>
@@ -1315,8 +1293,10 @@
         <v>3</v>
       </c>
       <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
         <v>37</v>
       </c>
@@ -1336,8 +1316,10 @@
         <v>3</v>
       </c>
       <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
         <v>38</v>
       </c>
@@ -1357,8 +1339,10 @@
         <v>3</v>
       </c>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
         <v>39</v>
       </c>
@@ -1378,8 +1362,10 @@
         <v>3</v>
       </c>
       <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
         <v>40</v>
       </c>
@@ -1399,8 +1385,10 @@
         <v>3</v>
       </c>
       <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
         <v>41</v>
       </c>
@@ -1422,8 +1410,10 @@
       <c r="G22" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="2" t="s">
         <v>42</v>
       </c>
@@ -1443,8 +1433,10 @@
         <v>3</v>
       </c>
       <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="2" t="s">
         <v>43</v>
       </c>
@@ -1464,8 +1456,10 @@
         <v>3</v>
       </c>
       <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="2" t="s">
         <v>44</v>
       </c>
@@ -1485,8 +1479,10 @@
         <v>3</v>
       </c>
       <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="2" t="s">
         <v>45</v>
       </c>
@@ -1506,8 +1502,10 @@
         <v>3</v>
       </c>
       <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="2" t="s">
         <v>46</v>
       </c>
@@ -1527,8 +1525,10 @@
         <v>15</v>
       </c>
       <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="2" t="s">
         <v>47</v>
       </c>
@@ -1548,8 +1548,10 @@
         <v>15</v>
       </c>
       <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="2" t="s">
         <v>48</v>
       </c>
@@ -1569,8 +1571,10 @@
         <v>15</v>
       </c>
       <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="2" t="s">
         <v>49</v>
       </c>
@@ -1590,8 +1594,10 @@
         <v>15</v>
       </c>
       <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="2" t="s">
         <v>50</v>
       </c>
@@ -1611,8 +1617,10 @@
         <v>15</v>
       </c>
       <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="2" t="s">
         <v>51</v>
       </c>
@@ -1632,8 +1640,10 @@
         <v>15</v>
       </c>
       <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="2" t="s">
         <v>52</v>
       </c>
@@ -1655,8 +1665,10 @@
       <c r="G33" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="2" t="s">
         <v>53</v>
       </c>
@@ -1676,8 +1688,10 @@
         <v>15</v>
       </c>
       <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="2" t="s">
         <v>54</v>
       </c>
@@ -1697,8 +1711,10 @@
         <v>15</v>
       </c>
       <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="2" t="s">
         <v>55</v>
       </c>
@@ -1718,8 +1734,10 @@
         <v>15</v>
       </c>
       <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="2" t="s">
         <v>56</v>
       </c>
@@ -1739,8 +1757,10 @@
         <v>15</v>
       </c>
       <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="2" t="s">
         <v>57</v>
       </c>
@@ -1760,8 +1780,10 @@
         <v>15</v>
       </c>
       <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="2" t="s">
         <v>58</v>
       </c>
@@ -1781,8 +1803,10 @@
         <v>15</v>
       </c>
       <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="2" t="s">
         <v>59</v>
       </c>
@@ -1802,8 +1826,10 @@
         <v>15</v>
       </c>
       <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="2" t="s">
         <v>60</v>
       </c>
@@ -1823,8 +1849,10 @@
         <v>15</v>
       </c>
       <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="2" t="s">
         <v>61</v>
       </c>
@@ -1844,8 +1872,10 @@
         <v>15</v>
       </c>
       <c r="G42" s="2"/>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="2" t="s">
         <v>62</v>
       </c>
@@ -1865,8 +1895,10 @@
         <v>15</v>
       </c>
       <c r="G43" s="2"/>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="2" t="s">
         <v>63</v>
       </c>
@@ -1886,8 +1918,10 @@
         <v>15</v>
       </c>
       <c r="G44" s="2"/>
-    </row>
-    <row r="45" spans="1:7">
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="2" t="s">
         <v>64</v>
       </c>
@@ -1907,8 +1941,10 @@
         <v>15</v>
       </c>
       <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="1:7">
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="2" t="s">
         <v>65</v>
       </c>
@@ -1928,8 +1964,10 @@
         <v>15</v>
       </c>
       <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="1:7">
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="2" t="s">
         <v>66</v>
       </c>
@@ -1949,8 +1987,10 @@
         <v>15</v>
       </c>
       <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="1:7">
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="2" t="s">
         <v>67</v>
       </c>
@@ -1970,8 +2010,10 @@
         <v>15</v>
       </c>
       <c r="G48" s="2"/>
-    </row>
-    <row r="49" spans="1:7">
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="2" t="s">
         <v>68</v>
       </c>
@@ -1991,8 +2033,10 @@
         <v>15</v>
       </c>
       <c r="G49" s="2"/>
-    </row>
-    <row r="50" spans="1:7">
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="2" t="s">
         <v>69</v>
       </c>
@@ -2012,8 +2056,10 @@
         <v>15</v>
       </c>
       <c r="G50" s="2"/>
-    </row>
-    <row r="51" spans="1:7">
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="5" t="s">
         <v>70</v>
       </c>
@@ -2033,8 +2079,10 @@
         <v>15</v>
       </c>
       <c r="G51" s="2"/>
-    </row>
-    <row r="52" spans="1:7">
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="2" t="s">
         <v>71</v>
       </c>
@@ -2054,8 +2102,10 @@
         <v>15</v>
       </c>
       <c r="G52" s="2"/>
-    </row>
-    <row r="53" spans="1:7">
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="2" t="s">
         <v>72</v>
       </c>
@@ -2075,8 +2125,10 @@
         <v>15</v>
       </c>
       <c r="G53" s="2"/>
-    </row>
-    <row r="54" spans="1:7">
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="2" t="s">
         <v>73</v>
       </c>
@@ -2096,8 +2148,10 @@
         <v>15</v>
       </c>
       <c r="G54" s="2"/>
-    </row>
-    <row r="55" spans="1:7">
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="2" t="s">
         <v>74</v>
       </c>
@@ -2117,8 +2171,10 @@
         <v>15</v>
       </c>
       <c r="G55" s="2"/>
-    </row>
-    <row r="56" spans="1:7">
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="2" t="s">
         <v>75</v>
       </c>
@@ -2138,8 +2194,10 @@
         <v>15</v>
       </c>
       <c r="G56" s="2"/>
-    </row>
-    <row r="57" spans="1:7">
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="2" t="s">
         <v>76</v>
       </c>
@@ -2159,8 +2217,10 @@
         <v>15</v>
       </c>
       <c r="G57" s="2"/>
-    </row>
-    <row r="58" spans="1:7">
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="2" t="s">
         <v>77</v>
       </c>
@@ -2180,8 +2240,10 @@
         <v>15</v>
       </c>
       <c r="G58" s="2"/>
-    </row>
-    <row r="59" spans="1:7">
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" s="2" t="s">
         <v>78</v>
       </c>
@@ -2201,8 +2263,10 @@
         <v>15</v>
       </c>
       <c r="G59" s="2"/>
-    </row>
-    <row r="60" spans="1:7">
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" s="2" t="s">
         <v>79</v>
       </c>
@@ -2222,8 +2286,10 @@
         <v>15</v>
       </c>
       <c r="G60" s="2"/>
-    </row>
-    <row r="61" spans="1:7">
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="2" t="s">
         <v>41</v>
       </c>
@@ -2243,8 +2309,10 @@
         <v>15</v>
       </c>
       <c r="G61" s="2"/>
-    </row>
-    <row r="62" spans="1:7">
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="2" t="s">
         <v>80</v>
       </c>
@@ -2264,8 +2332,10 @@
         <v>15</v>
       </c>
       <c r="G62" s="2"/>
-    </row>
-    <row r="63" spans="1:7">
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" s="2" t="s">
         <v>81</v>
       </c>
@@ -2285,8 +2355,10 @@
         <v>15</v>
       </c>
       <c r="G63" s="2"/>
-    </row>
-    <row r="64" spans="1:7">
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" s="2" t="s">
         <v>82</v>
       </c>
@@ -2306,8 +2378,10 @@
         <v>15</v>
       </c>
       <c r="G64" s="2"/>
-    </row>
-    <row r="65" spans="1:7">
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" s="6" t="s">
         <v>83</v>
       </c>
@@ -2327,8 +2401,10 @@
         <v>15</v>
       </c>
       <c r="G65" s="2"/>
-    </row>
-    <row r="66" spans="1:7">
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" s="6" t="s">
         <v>84</v>
       </c>
@@ -2348,8 +2424,10 @@
         <v>15</v>
       </c>
       <c r="G66" s="2"/>
-    </row>
-    <row r="67" spans="1:7">
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" s="6" t="s">
         <v>85</v>
       </c>
@@ -2369,8 +2447,10 @@
         <v>15</v>
       </c>
       <c r="G67" s="2"/>
-    </row>
-    <row r="68" spans="1:7">
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" s="6" t="s">
         <v>86</v>
       </c>
@@ -2390,8 +2470,10 @@
         <v>15</v>
       </c>
       <c r="G68" s="2"/>
-    </row>
-    <row r="69" spans="1:7">
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69" s="6" t="s">
         <v>87</v>
       </c>
@@ -2411,8 +2493,10 @@
         <v>15</v>
       </c>
       <c r="G69" s="2"/>
-    </row>
-    <row r="70" spans="1:7">
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70" s="6" t="s">
         <v>88</v>
       </c>
@@ -2432,8 +2516,10 @@
         <v>15</v>
       </c>
       <c r="G70" s="2"/>
-    </row>
-    <row r="71" spans="1:7">
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71" s="6" t="s">
         <v>89</v>
       </c>
@@ -2453,8 +2539,10 @@
         <v>15</v>
       </c>
       <c r="G71" s="2"/>
-    </row>
-    <row r="72" spans="1:7">
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72" s="6" t="s">
         <v>90</v>
       </c>
@@ -2474,8 +2562,10 @@
         <v>15</v>
       </c>
       <c r="G72" s="2"/>
-    </row>
-    <row r="73" spans="1:7">
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+    </row>
+    <row r="73" spans="1:9">
       <c r="A73" s="6" t="s">
         <v>91</v>
       </c>
@@ -2495,8 +2585,10 @@
         <v>15</v>
       </c>
       <c r="G73" s="2"/>
-    </row>
-    <row r="74" spans="1:7">
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74" s="6" t="s">
         <v>92</v>
       </c>
@@ -2516,8 +2608,10 @@
         <v>15</v>
       </c>
       <c r="G74" s="2"/>
-    </row>
-    <row r="75" spans="1:7">
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+    </row>
+    <row r="75" spans="1:9">
       <c r="A75" s="6" t="s">
         <v>93</v>
       </c>
@@ -2537,8 +2631,10 @@
         <v>15</v>
       </c>
       <c r="G75" s="2"/>
-    </row>
-    <row r="76" spans="1:7">
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+    </row>
+    <row r="76" spans="1:9">
       <c r="A76" s="6" t="s">
         <v>94</v>
       </c>
@@ -2558,8 +2654,10 @@
         <v>15</v>
       </c>
       <c r="G76" s="2"/>
-    </row>
-    <row r="77" spans="1:7">
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+    </row>
+    <row r="77" spans="1:9">
       <c r="A77" s="6" t="s">
         <v>95</v>
       </c>
@@ -2579,8 +2677,10 @@
         <v>15</v>
       </c>
       <c r="G77" s="2"/>
-    </row>
-    <row r="78" spans="1:7">
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+    </row>
+    <row r="78" spans="1:9">
       <c r="A78" s="6" t="s">
         <v>96</v>
       </c>
@@ -2600,8 +2700,10 @@
         <v>15</v>
       </c>
       <c r="G78" s="2"/>
-    </row>
-    <row r="79" spans="1:7">
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+    </row>
+    <row r="79" spans="1:9">
       <c r="A79" s="6" t="s">
         <v>97</v>
       </c>
@@ -2621,8 +2723,10 @@
         <v>15</v>
       </c>
       <c r="G79" s="2"/>
-    </row>
-    <row r="80" spans="1:7">
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+    </row>
+    <row r="80" spans="1:9">
       <c r="A80" s="6" t="s">
         <v>98</v>
       </c>
@@ -2642,8 +2746,10 @@
         <v>15</v>
       </c>
       <c r="G80" s="2"/>
-    </row>
-    <row r="81" spans="1:7">
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+    </row>
+    <row r="81" spans="1:9">
       <c r="A81" s="6" t="s">
         <v>99</v>
       </c>
@@ -2663,8 +2769,10 @@
         <v>15</v>
       </c>
       <c r="G81" s="2"/>
-    </row>
-    <row r="82" spans="1:7">
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+    </row>
+    <row r="82" spans="1:9">
       <c r="A82" s="6" t="s">
         <v>100</v>
       </c>
@@ -2684,8 +2792,10 @@
         <v>15</v>
       </c>
       <c r="G82" s="2"/>
-    </row>
-    <row r="83" spans="1:7">
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83" s="6" t="s">
         <v>101</v>
       </c>
@@ -2705,8 +2815,10 @@
         <v>15</v>
       </c>
       <c r="G83" s="2"/>
-    </row>
-    <row r="84" spans="1:7">
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+    </row>
+    <row r="84" spans="1:9">
       <c r="A84" s="6" t="s">
         <v>102</v>
       </c>
@@ -2726,8 +2838,10 @@
         <v>15</v>
       </c>
       <c r="G84" s="2"/>
-    </row>
-    <row r="85" spans="1:7">
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+    </row>
+    <row r="85" spans="1:9">
       <c r="A85" s="6" t="s">
         <v>103</v>
       </c>
@@ -2747,8 +2861,10 @@
         <v>15</v>
       </c>
       <c r="G85" s="2"/>
-    </row>
-    <row r="86" spans="1:7">
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+    </row>
+    <row r="86" spans="1:9">
       <c r="A86" s="6" t="s">
         <v>104</v>
       </c>
@@ -2768,8 +2884,10 @@
         <v>15</v>
       </c>
       <c r="G86" s="2"/>
-    </row>
-    <row r="87" spans="1:7">
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+    </row>
+    <row r="87" spans="1:9">
       <c r="A87" s="6" t="s">
         <v>105</v>
       </c>
@@ -2789,8 +2907,10 @@
         <v>15</v>
       </c>
       <c r="G87" s="2"/>
-    </row>
-    <row r="88" spans="1:7">
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+    </row>
+    <row r="88" spans="1:9">
       <c r="A88" s="6" t="s">
         <v>106</v>
       </c>
@@ -2810,8 +2930,10 @@
         <v>15</v>
       </c>
       <c r="G88" s="2"/>
-    </row>
-    <row r="89" spans="1:7">
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+    </row>
+    <row r="89" spans="1:9">
       <c r="A89" s="6" t="s">
         <v>107</v>
       </c>
@@ -2831,8 +2953,10 @@
         <v>15</v>
       </c>
       <c r="G89" s="2"/>
-    </row>
-    <row r="90" spans="1:7">
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+    </row>
+    <row r="90" spans="1:9">
       <c r="A90" s="6" t="s">
         <v>108</v>
       </c>
@@ -2852,8 +2976,10 @@
         <v>15</v>
       </c>
       <c r="G90" s="2"/>
-    </row>
-    <row r="91" spans="1:7">
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+    </row>
+    <row r="91" spans="1:9">
       <c r="A91" s="6" t="s">
         <v>109</v>
       </c>
@@ -2873,8 +2999,10 @@
         <v>15</v>
       </c>
       <c r="G91" s="2"/>
-    </row>
-    <row r="92" spans="1:7">
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+    </row>
+    <row r="92" spans="1:9">
       <c r="A92" s="6" t="s">
         <v>110</v>
       </c>
@@ -2894,8 +3022,10 @@
         <v>15</v>
       </c>
       <c r="G92" s="2"/>
-    </row>
-    <row r="93" spans="1:7">
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+    </row>
+    <row r="93" spans="1:9">
       <c r="A93" s="6" t="s">
         <v>111</v>
       </c>
@@ -2915,8 +3045,10 @@
         <v>15</v>
       </c>
       <c r="G93" s="2"/>
-    </row>
-    <row r="94" spans="1:7">
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+    </row>
+    <row r="94" spans="1:9">
       <c r="A94" s="6" t="s">
         <v>112</v>
       </c>
@@ -2936,8 +3068,10 @@
         <v>15</v>
       </c>
       <c r="G94" s="2"/>
-    </row>
-    <row r="95" spans="1:7">
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+    </row>
+    <row r="95" spans="1:9">
       <c r="A95" s="6" t="s">
         <v>113</v>
       </c>
@@ -2957,8 +3091,10 @@
         <v>15</v>
       </c>
       <c r="G95" s="2"/>
-    </row>
-    <row r="96" spans="1:7">
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+    </row>
+    <row r="96" spans="1:9">
       <c r="A96" s="6" t="s">
         <v>114</v>
       </c>
@@ -2978,8 +3114,10 @@
         <v>15</v>
       </c>
       <c r="G96" s="2"/>
-    </row>
-    <row r="97" spans="1:7">
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+    </row>
+    <row r="97" spans="1:9">
       <c r="A97" s="6" t="s">
         <v>115</v>
       </c>
@@ -2999,8 +3137,10 @@
         <v>15</v>
       </c>
       <c r="G97" s="2"/>
-    </row>
-    <row r="98" spans="1:7">
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+    </row>
+    <row r="98" spans="1:9">
       <c r="A98" s="6" t="s">
         <v>116</v>
       </c>
@@ -3020,8 +3160,10 @@
         <v>15</v>
       </c>
       <c r="G98" s="2"/>
-    </row>
-    <row r="99" spans="1:7">
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+    </row>
+    <row r="99" spans="1:9">
       <c r="A99" s="6" t="s">
         <v>117</v>
       </c>
@@ -3041,8 +3183,10 @@
         <v>15</v>
       </c>
       <c r="G99" s="2"/>
-    </row>
-    <row r="100" spans="1:7">
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+    </row>
+    <row r="100" spans="1:9">
       <c r="A100" s="6" t="s">
         <v>118</v>
       </c>
@@ -3062,8 +3206,10 @@
         <v>15</v>
       </c>
       <c r="G100" s="2"/>
-    </row>
-    <row r="101" spans="1:7">
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+    </row>
+    <row r="101" spans="1:9">
       <c r="A101" s="6" t="s">
         <v>119</v>
       </c>
@@ -3083,8 +3229,10 @@
         <v>15</v>
       </c>
       <c r="G101" s="2"/>
-    </row>
-    <row r="102" spans="1:7">
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+    </row>
+    <row r="102" spans="1:9">
       <c r="A102" s="6" t="s">
         <v>120</v>
       </c>
@@ -3104,8 +3252,10 @@
         <v>15</v>
       </c>
       <c r="G102" s="2"/>
-    </row>
-    <row r="103" spans="1:7">
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+    </row>
+    <row r="103" spans="1:9">
       <c r="A103" s="6" t="s">
         <v>121</v>
       </c>
@@ -3125,8 +3275,10 @@
         <v>15</v>
       </c>
       <c r="G103" s="2"/>
-    </row>
-    <row r="104" spans="1:7">
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
+    </row>
+    <row r="104" spans="1:9">
       <c r="A104" s="6" t="s">
         <v>122</v>
       </c>
@@ -3146,8 +3298,10 @@
         <v>15</v>
       </c>
       <c r="G104" s="2"/>
-    </row>
-    <row r="105" spans="1:7">
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+    </row>
+    <row r="105" spans="1:9">
       <c r="A105" s="6" t="s">
         <v>123</v>
       </c>
@@ -3167,8 +3321,10 @@
         <v>15</v>
       </c>
       <c r="G105" s="2"/>
-    </row>
-    <row r="106" spans="1:7">
+      <c r="H105" s="2"/>
+      <c r="I105" s="2"/>
+    </row>
+    <row r="106" spans="1:9">
       <c r="A106" s="6" t="s">
         <v>124</v>
       </c>
@@ -3188,8 +3344,10 @@
         <v>15</v>
       </c>
       <c r="G106" s="2"/>
-    </row>
-    <row r="107" spans="1:7">
+      <c r="H106" s="2"/>
+      <c r="I106" s="2"/>
+    </row>
+    <row r="107" spans="1:9">
       <c r="A107" s="6" t="s">
         <v>32</v>
       </c>
@@ -3209,8 +3367,10 @@
         <v>15</v>
       </c>
       <c r="G107" s="2"/>
-    </row>
-    <row r="108" spans="1:7">
+      <c r="H107" s="2"/>
+      <c r="I107" s="2"/>
+    </row>
+    <row r="108" spans="1:9">
       <c r="A108" s="6" t="s">
         <v>125</v>
       </c>
@@ -3230,8 +3390,10 @@
         <v>15</v>
       </c>
       <c r="G108" s="2"/>
-    </row>
-    <row r="109" spans="1:7">
+      <c r="H108" s="2"/>
+      <c r="I108" s="2"/>
+    </row>
+    <row r="109" spans="1:9">
       <c r="A109" s="6" t="s">
         <v>126</v>
       </c>
@@ -3251,8 +3413,10 @@
         <v>15</v>
       </c>
       <c r="G109" s="2"/>
-    </row>
-    <row r="110" spans="1:7">
+      <c r="H109" s="2"/>
+      <c r="I109" s="2"/>
+    </row>
+    <row r="110" spans="1:9">
       <c r="A110" s="6" t="s">
         <v>127</v>
       </c>
@@ -3272,8 +3436,10 @@
         <v>15</v>
       </c>
       <c r="G110" s="2"/>
-    </row>
-    <row r="111" spans="1:7">
+      <c r="H110" s="2"/>
+      <c r="I110" s="2"/>
+    </row>
+    <row r="111" spans="1:9">
       <c r="A111" s="6" t="s">
         <v>128</v>
       </c>
@@ -3293,8 +3459,10 @@
         <v>15</v>
       </c>
       <c r="G111" s="2"/>
-    </row>
-    <row r="112" spans="1:7">
+      <c r="H111" s="2"/>
+      <c r="I111" s="2"/>
+    </row>
+    <row r="112" spans="1:9">
       <c r="A112" s="6" t="s">
         <v>129</v>
       </c>
@@ -3314,6 +3482,8 @@
         <v>15</v>
       </c>
       <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+      <c r="I112" s="2"/>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" s="6" t="s">
@@ -3335,6 +3505,8 @@
         <v>15</v>
       </c>
       <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
+      <c r="I113" s="2"/>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" s="6" t="s">
@@ -3356,6 +3528,8 @@
         <v>15</v>
       </c>
       <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+      <c r="I114" s="2"/>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" s="6" t="s">
@@ -3377,6 +3551,8 @@
         <v>15</v>
       </c>
       <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
+      <c r="I115" s="2"/>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="6" t="s">
@@ -3398,6 +3574,8 @@
         <v>15</v>
       </c>
       <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
+      <c r="I116" s="2"/>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" s="6" t="s">
@@ -3419,6 +3597,8 @@
         <v>15</v>
       </c>
       <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
+      <c r="I117" s="2"/>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="6" t="s">
@@ -3440,6 +3620,8 @@
         <v>15</v>
       </c>
       <c r="G118" s="2"/>
+      <c r="H118" s="2"/>
+      <c r="I118" s="2"/>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" s="6" t="s">
@@ -3461,6 +3643,8 @@
         <v>15</v>
       </c>
       <c r="G119" s="2"/>
+      <c r="H119" s="2"/>
+      <c r="I119" s="2"/>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" s="6" t="s">
@@ -3482,16 +3666,34 @@
         <v>15</v>
       </c>
       <c r="G120" s="2"/>
+      <c r="H120" s="2"/>
+      <c r="I120" s="2"/>
     </row>
     <row r="121" spans="1:9">
-      <c r="A121" s="11" t="s">
+      <c r="A121" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C121" s="6">
+        <v>2019</v>
+      </c>
+      <c r="D121" s="9">
+        <v>43466</v>
+      </c>
+      <c r="E121" s="9">
+        <v>43466</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G121" s="2"/>
+      <c r="H121" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="H121" t="s">
+      <c r="I121" s="10" t="s">
         <v>141</v>
-      </c>
-      <c r="I121" s="12" t="s">
-        <v>142</v>
       </c>
     </row>
   </sheetData>
